--- a/branches/releasecandidate/all-profiles.xlsx
+++ b/branches/releasecandidate/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-15T15:53:54+00:00</t>
+    <t>2025-04-16T11:48:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/releasecandidate/all-profiles.xlsx
+++ b/branches/releasecandidate/all-profiles.xlsx
@@ -51,7 +51,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -60,22 +60,22 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-16T11:48:51+00:00</t>
+    <t>2025-04-16T12:31:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>HL7 Belgium</t>
+    <t>eHealth Platform Belgium</t>
   </si>
   <si>
     <t>Contact</t>
   </si>
   <si>
-    <t>HL7 Belgium (https://www.hl7belgium.org, hl7belgium@hl7belgium.org)</t>
-  </si>
-  <si>
-    <t>Message Structure eHealth (message-structure@ehealth.fgov.be(work))</t>
+    <t>eHealth Platform Belgium (https://www.ehealth.fgov.be/standards/fhir/, support@be-ehealth-standards.atlassian.net)</t>
+  </si>
+  <si>
+    <t>Message Structure eHealth (support@be-ehealth-standards.atlassian.net(work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/branches/releasecandidate/all-profiles.xlsx
+++ b/branches/releasecandidate/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-16T12:31:30+00:00</t>
+    <t>2025-04-16T12:36:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/releasecandidate/all-profiles.xlsx
+++ b/branches/releasecandidate/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-16T12:36:28+00:00</t>
+    <t>2025-04-16T12:41:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/releasecandidate/all-profiles.xlsx
+++ b/branches/releasecandidate/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-16T12:41:18+00:00</t>
+    <t>2025-04-16T13:08:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/releasecandidate/all-profiles.xlsx
+++ b/branches/releasecandidate/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-28T07:30:51+00:00</t>
+    <t>2025-04-28T07:57:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/releasecandidate/all-profiles.xlsx
+++ b/branches/releasecandidate/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-28T07:57:44+00:00</t>
+    <t>2025-04-30T14:16:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/releasecandidate/all-profiles.xlsx
+++ b/branches/releasecandidate/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-30T14:16:39+00:00</t>
+    <t>2025-05-06T09:47:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/releasecandidate/all-profiles.xlsx
+++ b/branches/releasecandidate/all-profiles.xlsx
@@ -66,22 +66,22 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-13T11:55:17+00:00</t>
+    <t>2025-05-14T06:43:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>eHealth Platform Belgium</t>
+    <t>eHealth Platform</t>
   </si>
   <si>
     <t>Contact</t>
   </si>
   <si>
-    <t>eHealth Platform Belgium (https://www.ehealth.fgov.be/standards/fhir/, support@be-ehealth-standards.atlassian.net)</t>
-  </si>
-  <si>
-    <t>Message Structure eHealth (support@be-ehealth-standards.atlassian.net(Work))</t>
+    <t>eHealth Platform (http://www.ehealth.fgov.be/, support@be-ehealth-standards.atlassian.net)</t>
+  </si>
+  <si>
+    <t>Message Structure (support@be-ehealth-standards.atlassian.net(Work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/branches/releasecandidate/all-profiles.xlsx
+++ b/branches/releasecandidate/all-profiles.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-14T06:43:44+00:00</t>
+    <t>2025-05-14T07:38:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/releasecandidate/all-profiles.xlsx
+++ b/branches/releasecandidate/all-profiles.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-14T07:38:16+00:00</t>
+    <t>2025-05-14T08:06:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/releasecandidate/all-profiles.xlsx
+++ b/branches/releasecandidate/all-profiles.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-14T08:06:44+00:00</t>
+    <t>2025-05-14T08:53:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
